--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q10_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00176622813090225</v>
+        <v>0.001771924945957386</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00176622813090225</v>
+        <v>0.001771924945957386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002251416430680424</v>
+        <v>0.002804646682166134</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001752094573764491</v>
+        <v>0.001751330146471047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001752094573764491</v>
+        <v>0.001751330146471047</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002073967567399497</v>
+        <v>0.002547997506795757</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00172607545842734</v>
+        <v>0.001716565814670754</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00172607545842734</v>
+        <v>0.001716565814670754</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001883279672609299</v>
+        <v>0.002260550029631856</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001679394076484119</v>
+        <v>0.001660651861964985</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001679394076484119</v>
+        <v>0.001660651861964985</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001668662252567936</v>
+        <v>0.001956589700895452</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001631697488118094</v>
+        <v>0.001605439986032534</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001631697488118094</v>
+        <v>0.001605439986032534</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00146002371258208</v>
+        <v>0.001675292224622394</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.00159543018257969</v>
+        <v>0.001564521750953848</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00159543018257969</v>
+        <v>0.001564521750953848</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001277645830910401</v>
+        <v>0.001434657572584469</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001576255448819114</v>
+        <v>0.001543657355286894</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001576255448819114</v>
+        <v>0.001543657355286894</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001124655874074246</v>
+        <v>0.001231837718255404</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001580628738165266</v>
+        <v>0.001549086696553542</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001580628738165266</v>
+        <v>0.001549086696553542</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001004405926650674</v>
+        <v>0.001067419924210486</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001602397642848086</v>
+        <v>0.001574324832910117</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001602397642848086</v>
+        <v>0.001574324832910117</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0009200196927414932</v>
+        <v>0.0009443979592304653</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001683367446363108</v>
+        <v>0.001660747934944044</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001683367446363108</v>
+        <v>0.001660747934944044</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0008778515978744346</v>
+        <v>0.0008761119194987992</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001797424494873892</v>
+        <v>0.001781885019076015</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001797424494873892</v>
+        <v>0.001781885019076015</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008803165816553112</v>
+        <v>0.0008722141789811676</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001959855521659451</v>
+        <v>0.0019527338682372</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001959855521659451</v>
+        <v>0.0019527338682372</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00093411306279312</v>
+        <v>0.000942146823323562</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00218349466474798</v>
+        <v>0.002185966157414945</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00218349466474798</v>
+        <v>0.002185966157414945</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001043319803126826</v>
+        <v>0.001077858199150477</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002449144340865479</v>
+        <v>0.002461749756890142</v>
       </c>
       <c r="C15" t="n">
-        <v>0.002449144340865479</v>
+        <v>0.002461749756890142</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001214003013614045</v>
+        <v>0.001281140126948755</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002762360055300599</v>
+        <v>0.002785203682257615</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002762360055300599</v>
+        <v>0.002785203682257615</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001448451554784598</v>
+        <v>0.001555138335073965</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003114297325657707</v>
+        <v>0.003146743889483305</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003114297325657707</v>
+        <v>0.003146743889483305</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001748058642904353</v>
+        <v>0.001901746413705655</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003488618952730521</v>
+        <v>0.003529013897941305</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003488618952730521</v>
+        <v>0.003529013897941305</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002106568411586611</v>
+        <v>0.002314933865829945</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003892567133052648</v>
+        <v>0.003938636613879003</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003892567133052648</v>
+        <v>0.003938636613879003</v>
       </c>
       <c r="D19" t="n">
-        <v>0.002491615741817516</v>
+        <v>0.002755581386492383</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.004314417760867603</v>
+        <v>0.004363293680746039</v>
       </c>
       <c r="C20" t="n">
-        <v>0.004314417760867603</v>
+        <v>0.004363293680746039</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002858656825899451</v>
+        <v>0.003152653628494772</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.004732399871645704</v>
+        <v>0.004780768912034045</v>
       </c>
       <c r="C21" t="n">
-        <v>0.004732399871645704</v>
+        <v>0.004780768912034045</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003167648882537646</v>
+        <v>0.00349540302040079</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.005136651444953367</v>
+        <v>0.00518158162806744</v>
       </c>
       <c r="C22" t="n">
-        <v>0.005136651444953367</v>
+        <v>0.00518158162806744</v>
       </c>
       <c r="D22" t="n">
-        <v>0.003357202492687411</v>
+        <v>0.0036955093988028</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.005531345855958509</v>
+        <v>0.005571038040278239</v>
       </c>
       <c r="C23" t="n">
-        <v>0.005531345855958509</v>
+        <v>0.005571038040278239</v>
       </c>
       <c r="D23" t="n">
-        <v>0.003433675076526169</v>
+        <v>0.003774355781152484</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.005943161495069884</v>
+        <v>0.00597746057624274</v>
       </c>
       <c r="C24" t="n">
-        <v>0.005943161495069884</v>
+        <v>0.00597746057624274</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003442534869392425</v>
+        <v>0.003786983759904964</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.006391918403411453</v>
+        <v>0.006422735538413358</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006391918403411453</v>
+        <v>0.006422735538413358</v>
       </c>
       <c r="D25" t="n">
-        <v>0.003447284799861867</v>
+        <v>0.003805966945848921</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.006895029099510393</v>
+        <v>0.006925548787508785</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006895029099510393</v>
+        <v>0.006925548787508785</v>
       </c>
       <c r="D26" t="n">
-        <v>0.003492242486237242</v>
+        <v>0.003882846785881778</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.00744040545055604</v>
+        <v>0.007473847947588597</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00744040545055604</v>
+        <v>0.007473847947588597</v>
       </c>
       <c r="D27" t="n">
-        <v>0.003592957213592849</v>
+        <v>0.004034383055341612</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.008020815715071718</v>
+        <v>0.008060751575772376</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008020815715071718</v>
+        <v>0.008060751575772376</v>
       </c>
       <c r="D28" t="n">
-        <v>0.003757360959007995</v>
+        <v>0.004257028880996827</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.008612663477325016</v>
+        <v>0.008661754775718691</v>
       </c>
       <c r="C29" t="n">
-        <v>0.008612663477325016</v>
+        <v>0.008661754775718691</v>
       </c>
       <c r="D29" t="n">
-        <v>0.003965743257260782</v>
+        <v>0.004528925735526216</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.009191343405694857</v>
+        <v>0.009250865183177796</v>
       </c>
       <c r="C30" t="n">
-        <v>0.009191343405694857</v>
+        <v>0.009250865183177796</v>
       </c>
       <c r="D30" t="n">
-        <v>0.004197204453231722</v>
+        <v>0.00482283821347564</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.009757273840075886</v>
+        <v>0.00982784365362011</v>
       </c>
       <c r="C31" t="n">
-        <v>0.009757273840075886</v>
+        <v>0.00982784365362011</v>
       </c>
       <c r="D31" t="n">
-        <v>0.004436694180936061</v>
+        <v>0.005120429496243175</v>
       </c>
     </row>
   </sheetData>
